--- a/artfynd/A 38744-2024 artfynd.xlsx
+++ b/artfynd/A 38744-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819567</v>
+        <v>119819566</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777966</v>
+        <v>777917</v>
       </c>
       <c r="R2" t="n">
-        <v>7488948</v>
+        <v>7488955</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819566</v>
+        <v>119819567</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>78262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777917</v>
+        <v>777966</v>
       </c>
       <c r="R3" t="n">
-        <v>7488955</v>
+        <v>7488948</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 38744-2024 artfynd.xlsx
+++ b/artfynd/A 38744-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119819566</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819567</v>
+        <v>119819569</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>91870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777966</v>
+        <v>778103</v>
       </c>
       <c r="R3" t="n">
-        <v>7488948</v>
+        <v>7488971</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819569</v>
+        <v>119819567</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778103</v>
+        <v>777966</v>
       </c>
       <c r="R4" t="n">
-        <v>7488971</v>
+        <v>7488948</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 38744-2024 artfynd.xlsx
+++ b/artfynd/A 38744-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819566</v>
+        <v>119819567</v>
       </c>
       <c r="B2" t="n">
-        <v>91870</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777917</v>
+        <v>777966</v>
       </c>
       <c r="R2" t="n">
-        <v>7488955</v>
+        <v>7488948</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819569</v>
+        <v>119819566</v>
       </c>
       <c r="B3" t="n">
         <v>91870</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778103</v>
+        <v>777917</v>
       </c>
       <c r="R3" t="n">
-        <v>7488971</v>
+        <v>7488955</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819567</v>
+        <v>119819569</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>91870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777966</v>
+        <v>778103</v>
       </c>
       <c r="R4" t="n">
-        <v>7488948</v>
+        <v>7488971</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 38744-2024 artfynd.xlsx
+++ b/artfynd/A 38744-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819567</v>
+        <v>119819569</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>91870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777966</v>
+        <v>778103</v>
       </c>
       <c r="R2" t="n">
-        <v>7488948</v>
+        <v>7488971</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819569</v>
+        <v>119819567</v>
       </c>
       <c r="B4" t="n">
-        <v>91870</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778103</v>
+        <v>777966</v>
       </c>
       <c r="R4" t="n">
-        <v>7488971</v>
+        <v>7488948</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
